--- a/AAII_Financials/Quarterly/TAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>TAC</t>
   </si>
@@ -656,556 +656,569 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AQ102"/>
+  <dimension ref="A5:AR102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
-      <c r="AQ7" s="2">
+      <c r="AR7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>342900</v>
+      </c>
+      <c r="E8" s="3">
         <v>404800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>436900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>441500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>317500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>527400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>471200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>472300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>425200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>699300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>472500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>751800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>472000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>804900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>628600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>677000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>338500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>534400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>451600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1563700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>447700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>482100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>420900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>394100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>342900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>475700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>474800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>491600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>394100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>498800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>473400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>430900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>335700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>442600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>474800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>437600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>374300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>444000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>550800</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>476300</v>
       </c>
-      <c r="AQ8" s="3">
+      <c r="AR8" s="3">
         <v>378000</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>258600</v>
+        <v>156300</v>
       </c>
       <c r="E9" s="3">
+        <v>267200</v>
+      </c>
+      <c r="F9" s="3">
         <v>323100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>315900</v>
       </c>
-      <c r="G9" s="3">
-        <v>194300</v>
-      </c>
       <c r="H9" s="3">
-        <v>341600</v>
+        <v>198700</v>
       </c>
       <c r="I9" s="3">
+        <v>344400</v>
+      </c>
+      <c r="J9" s="3">
         <v>341900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>293100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>211900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>367000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>344500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>316400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>262000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>355500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>348200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>270400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>177400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>186800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>230300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>686700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>183700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>220000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>253000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>193200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>118500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>186800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>322000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>307600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>243500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>361800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>361500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>311000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>227300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>308600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>326000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>307400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>228500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>288100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>311100</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>322700</v>
       </c>
-      <c r="AQ9" s="3">
+      <c r="AR9" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>146100</v>
+        <v>186600</v>
       </c>
       <c r="E10" s="3">
+        <v>137500</v>
+      </c>
+      <c r="F10" s="3">
         <v>113800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>125600</v>
       </c>
-      <c r="G10" s="3">
-        <v>123200</v>
-      </c>
       <c r="H10" s="3">
-        <v>185800</v>
+        <v>118800</v>
       </c>
       <c r="I10" s="3">
+        <v>183000</v>
+      </c>
+      <c r="J10" s="3">
         <v>129300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>179100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>213300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>332300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>128000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>435400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>209900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>449400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>280500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>406600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>161100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>347500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>221400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>877000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>264000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>262100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>167900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>200900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>224400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>288900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>152800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>184000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>150700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>137000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>111900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>119900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>108400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>134000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>148800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>130200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>145900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>156000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>239700</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>153600</v>
       </c>
-      <c r="AQ10" s="3">
+      <c r="AR10" s="3">
         <v>150600</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1249,8 +1262,9 @@
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
       <c r="AQ11" s="3"/>
+      <c r="AR11" s="3"/>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1374,8 +1388,11 @@
       <c r="AQ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AR12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1499,258 +1516,267 @@
       <c r="AQ13" s="3">
         <v>0</v>
       </c>
+      <c r="AR13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>10000</v>
+        <v>12700</v>
       </c>
       <c r="E14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F14" s="3">
         <v>35000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>12900</v>
       </c>
-      <c r="G14" s="3">
-        <v>6600</v>
-      </c>
       <c r="H14" s="3">
-        <v>-13200</v>
+        <v>10300</v>
       </c>
       <c r="I14" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="J14" s="3">
         <v>27800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>5200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-13600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>51000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-17700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-30500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>20700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>885200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>11600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>21800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>13200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>58300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>25100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-32200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>36600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-18200</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>17500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>41400</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>3800</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>4500</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>14900</v>
       </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>21500</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>800</v>
       </c>
-      <c r="AQ14" s="3">
+      <c r="AR14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>73900</v>
+      </c>
+      <c r="E15" s="3">
         <v>75200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>107900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>96900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>110000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>101600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>99400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>98400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>95700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>91600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>100000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>103500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>130600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>130100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>138400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>130400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>85000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>85100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>99200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>292600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>89000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>111900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>133900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>124200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>127900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>122500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>120100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>122700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>113400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>111600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>115700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>106100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>109900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>97900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>134000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>117600</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>114600</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>109900</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>143700</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>111400</v>
       </c>
-      <c r="AQ15" s="3">
+      <c r="AR15" s="3">
         <v>112900</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1791,258 +1817,265 @@
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
       <c r="AQ16" s="3"/>
+      <c r="AR16" s="3"/>
     </row>
-    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>330300</v>
+        <v>228900</v>
       </c>
       <c r="E17" s="3">
+        <v>338900</v>
+      </c>
+      <c r="F17" s="3">
         <v>385800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>416400</v>
       </c>
-      <c r="G17" s="3">
-        <v>312300</v>
-      </c>
       <c r="H17" s="3">
-        <v>448000</v>
+        <v>308700</v>
       </c>
       <c r="I17" s="3">
+        <v>450800</v>
+      </c>
+      <c r="J17" s="3">
         <v>439200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>401900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>305400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>453400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>429300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>377700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>391900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>482600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>604300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>548000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>322900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>316200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>433100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1759300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>391300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>431700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>512200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>461500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>357800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>376800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>402300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>363100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>353700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>471100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>493200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>452000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>344800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>289800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>451000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>427200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>356500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>396400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>333400</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>440200</v>
       </c>
-      <c r="AQ17" s="3">
+      <c r="AR17" s="3">
         <v>346500</v>
       </c>
     </row>
-    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>74500</v>
+        <v>114100</v>
       </c>
       <c r="E18" s="3">
+        <v>65900</v>
+      </c>
+      <c r="F18" s="3">
         <v>51100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>25100</v>
       </c>
-      <c r="G18" s="3">
-        <v>5100</v>
-      </c>
       <c r="H18" s="3">
-        <v>79300</v>
+        <v>8800</v>
       </c>
       <c r="I18" s="3">
+        <v>76500</v>
+      </c>
+      <c r="J18" s="3">
         <v>32000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>70300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>119800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>245900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>43200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>374100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>80000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>322200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>24300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>129000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>15500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>218100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>18500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-195600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>56400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>50300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-91300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-67500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-14900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>98900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>72500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>128500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>40400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>27700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-19800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-21100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>152800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>23800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>10400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>17900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>47600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>217400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>36100</v>
       </c>
-      <c r="AQ18" s="3">
+      <c r="AR18" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2086,633 +2119,649 @@
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
       <c r="AQ19" s="3"/>
+      <c r="AR19" s="3"/>
     </row>
-    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-700</v>
+        <v>-4900</v>
       </c>
       <c r="E20" s="3">
         <v>-700</v>
       </c>
       <c r="F20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>11700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-13200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>12500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>8100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-7300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>53300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>28900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>11800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-22800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>74100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-18200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-22200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-6200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-9400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>8200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-3700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>9700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>4600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>18400</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>15400</v>
       </c>
-      <c r="AQ20" s="3">
+      <c r="AR20" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>150400</v>
+        <v>192900</v>
       </c>
       <c r="E21" s="3">
+        <v>141800</v>
+      </c>
+      <c r="F21" s="3">
         <v>159700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>123500</v>
       </c>
-      <c r="G21" s="3">
-        <v>103400</v>
-      </c>
       <c r="H21" s="3">
-        <v>179500</v>
+        <v>107000</v>
       </c>
       <c r="I21" s="3">
+        <v>176700</v>
+      </c>
+      <c r="J21" s="3">
         <v>144600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>163600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>217000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>334500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>153000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>469400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>216000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>451600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>175200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>255800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>108600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>295900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>120700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>283000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>210500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>207200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>89000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>85900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>144400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>220600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>290800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>257000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>155400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>155500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>117200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>100300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>122000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>269500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>180100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>137700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>156300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>175200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>394100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>175200</v>
       </c>
-      <c r="AQ21" s="3">
+      <c r="AR21" s="3">
         <v>162100</v>
       </c>
     </row>
-    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>59200</v>
+      </c>
+      <c r="E22" s="3">
         <v>58700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>59100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>61000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>64500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>64700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>63900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>61400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>58500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>51000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>90900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>39200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>54400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>54700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>31700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>33500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>39900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>34900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>37000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>115600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>33300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>38300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>40200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>35300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>37700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>40000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>35100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>38100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>37300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>31600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>32000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>33400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>39900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>42900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>40200</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>38700</v>
       </c>
       <c r="AM22" s="3">
         <v>38700</v>
       </c>
       <c r="AN22" s="3">
+        <v>38700</v>
+      </c>
+      <c r="AO22" s="3">
         <v>40700</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>41500</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>42300</v>
       </c>
-      <c r="AQ22" s="3">
+      <c r="AR22" s="3">
         <v>41500</v>
       </c>
     </row>
-    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E23" s="3">
         <v>16500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-30600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-38100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-69700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>34100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-35400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>68700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>197200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-26500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>334900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>59700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>283100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>91800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>175900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-23700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-257800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>52100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>15800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-130000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-98900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-40800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>36100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>111500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>72100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-57100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-63900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-55000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>105400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-8200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-32000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-11200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>11500</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>194400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>9200</v>
       </c>
-      <c r="AQ23" s="3">
+      <c r="AR23" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E24" s="3">
         <v>4300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-5600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>22900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>20500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>21400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>25100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-13600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>36200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>65500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>21900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>27300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>26200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>31100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>31800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>15000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-19300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-13300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>31200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>8300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-39700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>13100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-12200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-15300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-4500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>27900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>78100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-3700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-14100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-13100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>63000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-1500</v>
       </c>
-      <c r="AQ24" s="3">
+      <c r="AR24" s="3">
         <v>-18400</v>
       </c>
     </row>
-    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2836,258 +2885,267 @@
       <c r="AQ25" s="3">
         <v>0</v>
       </c>
+      <c r="AR25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E26" s="3">
         <v>12200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-29200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-38800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-77700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>29200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-29900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>48200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>175800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-40900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>309700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>73300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>246900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-60400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>70000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-43600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>149800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-25900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-288900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>20300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-110600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-91200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-27500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>34500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>80300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>63800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>20600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-23100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-44900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-48700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-50400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>77500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-86300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-28300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>3000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>24600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>131400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>10800</v>
       </c>
-      <c r="AQ26" s="3">
+      <c r="AR26" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E27" s="3">
         <v>9300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-45200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-44500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-82100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>32000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-45200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>40900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>163900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-63600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>275000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>46800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>217300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-120000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>44500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-59100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>135200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-57700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-368900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-22500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-129200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-104300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-47100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>21200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>51500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>42300</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
       <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-50000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-92900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-62500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-79000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>48900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-107900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-20100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-13400</v>
       </c>
-      <c r="AN27" s="3">
-        <v>0</v>
-      </c>
       <c r="AO27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP27" s="3">
         <v>46900</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-9200</v>
       </c>
-      <c r="AQ27" s="3">
+      <c r="AR27" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3211,8 +3269,11 @@
       <c r="AQ28" s="3">
         <v>0</v>
       </c>
+      <c r="AR28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3336,8 +3397,11 @@
       <c r="AQ29" s="3">
         <v>0</v>
       </c>
+      <c r="AR29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3461,8 +3525,11 @@
       <c r="AQ30" s="3">
         <v>0</v>
       </c>
+      <c r="AR30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3586,258 +3653,267 @@
       <c r="AQ31" s="3">
         <v>0</v>
       </c>
+      <c r="AR31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>700</v>
+        <v>4900</v>
       </c>
       <c r="E32" s="3">
         <v>700</v>
       </c>
       <c r="F32" s="3">
+        <v>700</v>
+      </c>
+      <c r="G32" s="3">
         <v>1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-11700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>13200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-12500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-8100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>7300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-53300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-28900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>22800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-74100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>18200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>22200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>6200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>5300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>9400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>4500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-8200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>3700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-9700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-4600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-18400</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-15400</v>
       </c>
-      <c r="AQ32" s="3">
+      <c r="AR32" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E33" s="3">
         <v>9300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-26300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-35200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-72600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>32000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-27100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>50400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>163900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-44700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>285300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>55900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>217300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-120000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>44500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-59100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>135200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-57700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-368900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-22500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-129200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-104300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-47100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>21200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>51500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>42300</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
       <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-50000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-92900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-62500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-79000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>48900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-107900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-20100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-13400</v>
       </c>
-      <c r="AN33" s="3">
-        <v>0</v>
-      </c>
       <c r="AO33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP33" s="3">
         <v>46900</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-9200</v>
       </c>
-      <c r="AQ33" s="3">
+      <c r="AR33" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3961,263 +4037,272 @@
       <c r="AQ34" s="3">
         <v>0</v>
       </c>
+      <c r="AR34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E35" s="3">
         <v>9300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-26300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-35200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-72600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>32000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-27100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>50400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>163900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-44700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>285300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>55900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>217300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-120000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>44500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-59100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>135200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-57700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-368900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-22500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-129200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-104300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-47100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>21200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>51500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>42300</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
       <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-50000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-92900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-62500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-79000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>48900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-107900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-20100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-13400</v>
       </c>
-      <c r="AN35" s="3">
-        <v>0</v>
-      </c>
       <c r="AO35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP35" s="3">
         <v>46900</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-9200</v>
       </c>
-      <c r="AQ35" s="3">
+      <c r="AR35" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
-      <c r="AQ38" s="2">
+      <c r="AR38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4261,8 +4346,9 @@
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
       <c r="AQ39" s="3"/>
+      <c r="AR39" s="3"/>
     </row>
-    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4306,133 +4392,137 @@
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
       <c r="AQ40" s="3"/>
+      <c r="AR40" s="3"/>
     </row>
-    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>212700</v>
+      </c>
+      <c r="E41" s="3">
         <v>196300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>149500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>151500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>162800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>165600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>234200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>296800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>256500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>309400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>263500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>910000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>718900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>921600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>834700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>594700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>663600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>887700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>701100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>800000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>464300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>486600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>543900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>207000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>201700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>265300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>320400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>270300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>164900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>83900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>67700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>69000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>92600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>247700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>233700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>64700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>37200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>387200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>234300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>120600</v>
       </c>
-      <c r="AQ41" s="3">
+      <c r="AR41" s="3">
         <v>71400</v>
       </c>
     </row>
-    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4476,59 +4566,59 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>521900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>550200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>445600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>373700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>228000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>303700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>162700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>123100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>132300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>147200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>215800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>208000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>129400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>132600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>130800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>107000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>111100</v>
       </c>
-      <c r="AH42" s="3">
-        <v>0</v>
-      </c>
       <c r="AI42" s="3">
         <v>0</v>
       </c>
@@ -4556,883 +4646,907 @@
       <c r="AQ42" s="3">
         <v>0</v>
       </c>
+      <c r="AR42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>464100</v>
+      </c>
+      <c r="E43" s="3">
         <v>416200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>442700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>488200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>480300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>504400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>446900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>579600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>364600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>383300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>501300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>490900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>597300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>598700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1169700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>967100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>758900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>394000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>482000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>382200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>502600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>426500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>451100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>371800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>335900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>338400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>360200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>374700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>399700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>562700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>575400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>472300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>423100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>505100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>694300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>829000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>499400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>504700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>480900</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>383300</v>
       </c>
-      <c r="AQ43" s="3">
+      <c r="AR43" s="3">
         <v>347200</v>
       </c>
     </row>
-    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E44" s="3">
         <v>84500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>81000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>99800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>99000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>92500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>93100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>116200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>113300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>111500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>118900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>133100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>151000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>106400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>115600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>124600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>115300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>112000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>123600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>137800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>150400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>162200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>184200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>197800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>233100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>206500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>195700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>202300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>212500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>174000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>184200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>191800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>211500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>168600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>163000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>173400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>183800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>152100</v>
-      </c>
-      <c r="AO44" s="3">
-        <v>163600</v>
       </c>
       <c r="AP44" s="3">
         <v>163600</v>
       </c>
       <c r="AQ44" s="3">
+        <v>163600</v>
+      </c>
+      <c r="AR44" s="3">
         <v>182800</v>
       </c>
     </row>
-    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>137300</v>
+      </c>
+      <c r="E45" s="3">
         <v>149000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>140000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>146500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>135600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>260200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>276600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>171700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>181900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>177200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>114300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>105700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>169900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>252800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>92000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>107100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>96800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>90900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>91800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>88100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>86800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>159900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>160200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>143400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>50200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>54200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>39800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>252900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>55500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>43100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>60100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>199100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>173100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>170900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>180800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>173400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>206900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>255800</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>315000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>227400</v>
       </c>
-      <c r="AQ45" s="3">
+      <c r="AR45" s="3">
         <v>226600</v>
       </c>
     </row>
-    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1004900</v>
+      </c>
+      <c r="E46" s="3">
         <v>992200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>974400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1046700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1058000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1224500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1232200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1251000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1107700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1188200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1196400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1855500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1946100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2042900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2733900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2343700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2080300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1858200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1626600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1711900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1366900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1358300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1471700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1067200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1036600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1072400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1045500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1232800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>963500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>970700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>998600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>932300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>900300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1092300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1271900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1240600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>927300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1299800</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1193800</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>895000</v>
       </c>
-      <c r="AQ46" s="3">
+      <c r="AR46" s="3">
         <v>828200</v>
       </c>
     </row>
-    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>208400</v>
+      </c>
+      <c r="E47" s="3">
         <v>202000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>207100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>193100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>176700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>175300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>110500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>109600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>107400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>106300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>104500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>101300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>104200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>96100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>189900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>195300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>203200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>202100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>214700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>217800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>216200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>238000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>253800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>125700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>131800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>135000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>137200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>148400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>145100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>144000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>145400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>142400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>152100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>157300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>160000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>171200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>500100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>535500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>552400</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>554700</v>
       </c>
-      <c r="AQ47" s="3">
+      <c r="AR47" s="3">
         <v>563100</v>
       </c>
     </row>
-    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4071500</v>
+      </c>
+      <c r="E48" s="3">
         <v>4148700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4212600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4208500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4335500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4200800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4267300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4189600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4187300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4266200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4415300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4285300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4373200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4295600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4182600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3928000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3873000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3841500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4009000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3918500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4133900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4347500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4613900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4627400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4776700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4883000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4953200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4956900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4850900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4703600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4691400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4506200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4787000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4869800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4895400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>4952000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>4989200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>5232400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>5242400</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>5354600</v>
       </c>
-      <c r="AQ48" s="3">
+      <c r="AR48" s="3">
         <v>5337700</v>
       </c>
     </row>
-    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>530200</v>
+      </c>
+      <c r="E49" s="3">
         <v>545200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>553600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>553500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>572600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>553100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>554600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>495200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>495400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>502900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>520200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>511600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>527900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>523300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>527100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>526200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>534300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>529300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>532300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>534800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>530800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>562400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>600400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>607200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>632500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>610800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>609700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>654100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>654200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>643600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>637000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>585000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>612000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>618800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>615500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>617700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>600600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>623000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>629200</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>630700</v>
       </c>
-      <c r="AQ49" s="3">
+      <c r="AR49" s="3">
         <v>631500</v>
       </c>
     </row>
-    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5556,8 +5670,11 @@
       <c r="AQ50" s="3">
         <v>0</v>
       </c>
+      <c r="AR50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5681,133 +5798,139 @@
       <c r="AQ51" s="3">
         <v>0</v>
       </c>
+      <c r="AR51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>135200</v>
+      </c>
+      <c r="E52" s="3">
         <v>121800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>105000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>124200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>128300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>179500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>161900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>180600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>165900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>211900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>129500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>162600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>155600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>208400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>273100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>327200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>393100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>420900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>447900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>520700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>525800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>566100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>602000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>648600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>775300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>711300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>667400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>685600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>681200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>719000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>703200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>680200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>770100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>761800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>725600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>729300</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>736800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>797400</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>829700</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>745200</v>
       </c>
-      <c r="AQ52" s="3">
+      <c r="AR52" s="3">
         <v>739800</v>
       </c>
     </row>
-    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5931,133 +6054,139 @@
       <c r="AQ53" s="3">
         <v>0</v>
       </c>
+      <c r="AR53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6226300</v>
+      </c>
+      <c r="E54" s="3">
         <v>6295000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6316700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6383800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6554200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6597600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6601800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6405900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6244100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6463200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6556700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7037500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7236100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7285200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7906600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7320400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7084000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6852100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6830600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6903700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6773700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7072400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7541700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7076100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7353000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7412400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7413100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7677800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7295000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7180900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7175600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6846100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7221500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7500000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>7668300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>7710800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>7753900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>8488200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>8447500</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>8180100</v>
       </c>
-      <c r="AQ54" s="3">
+      <c r="AR54" s="3">
         <v>8100200</v>
       </c>
     </row>
-    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -6101,8 +6230,9 @@
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
       <c r="AQ55" s="3"/>
+      <c r="AR55" s="3"/>
     </row>
-    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6146,758 +6276,777 @@
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
       <c r="AQ56" s="3"/>
+      <c r="AR56" s="3"/>
     </row>
-    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>363400</v>
+      </c>
+      <c r="E57" s="3">
         <v>358200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>399700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>407800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>365100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>469600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>482300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>437500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>346300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>445300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>584600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>492300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>487100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>574300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>990800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>932100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>846900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>611400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>510100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>573300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>420900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>469300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>463500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>390200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>314700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>324200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>322000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>296000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>288700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>352600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>378300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>346600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>319900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>373400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>442800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>380300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>313300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>351100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>317300</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>283500</v>
       </c>
-      <c r="AQ57" s="3">
+      <c r="AR57" s="3">
         <v>229700</v>
       </c>
     </row>
-    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>659100</v>
+      </c>
+      <c r="E58" s="3">
         <v>669800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>674600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>659800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>673100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>645600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>919500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>952700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>644400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>945300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>405100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>391100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>103500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>132300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>142800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>526200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>509900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>604900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>624900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>88100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>83200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>83300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>81200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>393300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>402600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>403500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>400000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>85400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>83300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>80800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>112600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>95900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>77500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>105400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>555900</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>686900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>701800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>484000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>490900</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>452500</v>
       </c>
-      <c r="AQ58" s="3">
+      <c r="AR58" s="3">
         <v>121400</v>
       </c>
     </row>
-    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>168300</v>
+      </c>
+      <c r="E59" s="3">
         <v>258600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>243600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>245500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>285200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>319300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>371800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>279100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>320000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>316800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>317300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>303800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>567900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>631200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>992300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>698900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>502500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>415800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>294700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>429600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>267600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>150200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>178700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>164800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>185200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>167200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>148900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>228000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>181600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>162400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>173500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>133000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>159600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>203300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>198000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>94500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>105700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>117500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>126800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>218900</v>
       </c>
-      <c r="AQ59" s="3">
+      <c r="AR59" s="3">
         <v>553100</v>
       </c>
     </row>
-    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1190800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1301700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1334700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1328200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1340300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1451300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1785500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1684000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1322500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1722900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1319100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1202700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1170500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1353300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2125900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2157100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1859300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1632100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1429600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1091100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>771700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>702800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>723500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>948300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>902500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>895000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>870900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>609400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>553500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>595800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>664400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>575500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>557100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>682000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1196700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1161700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1120800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>952600</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>934900</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>954900</v>
       </c>
-      <c r="AQ60" s="3">
+      <c r="AR60" s="3">
         <v>904200</v>
       </c>
     </row>
-    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2325900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2527500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2492900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2509900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2634400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2573500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2249000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2131100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2419200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2159300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2785000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2789100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3168700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3099800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3102000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2350300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2384000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2273400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2338100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2743700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2681700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2872800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3084200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2207200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2297700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2348900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2358500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2667100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2590000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2465700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2373800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2217100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2291500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2462400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2202900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2126200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2128400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2822500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2859400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2714200</v>
       </c>
-      <c r="AQ61" s="3">
+      <c r="AR61" s="3">
         <v>2710300</v>
       </c>
     </row>
-    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>966100</v>
+      </c>
+      <c r="E62" s="3">
         <v>950700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>989000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>941900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>889400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>829300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>841700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>763900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>649500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>674200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>775400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>618000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>691700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>705100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1214600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1051600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1012400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1027300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1143100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1103700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>982100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>961100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1075500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1030400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1020900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>952300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1016700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1080300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1015900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1026900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>990900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>940300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1021500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1029100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1005400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1091800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1081300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1118500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1070900</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1025600</v>
       </c>
-      <c r="AQ62" s="3">
+      <c r="AR62" s="3">
         <v>990200</v>
       </c>
     </row>
-    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -7021,8 +7170,11 @@
       <c r="AQ63" s="3">
         <v>0</v>
       </c>
+      <c r="AR63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -7146,8 +7298,11 @@
       <c r="AQ64" s="3">
         <v>0</v>
       </c>
+      <c r="AR64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7271,133 +7426,139 @@
       <c r="AQ65" s="3">
         <v>0</v>
       </c>
+      <c r="AR65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4924300</v>
+      </c>
+      <c r="E66" s="3">
         <v>5237600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5248300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5226500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5334900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5327900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5321000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4983900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4850800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5036500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5296700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5068900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5519600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5634800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7089500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6199600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5920800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5619800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5659300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5697000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5187700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5315300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5721900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5034500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5059200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5063600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5104500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5269400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5027700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4966100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4894600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4546200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4740300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4962400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5193100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5185700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>5167100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>5770900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>5750200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>5562000</v>
       </c>
-      <c r="AQ66" s="3">
+      <c r="AR66" s="3">
         <v>5469000</v>
       </c>
     </row>
-    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7441,8 +7602,9 @@
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
       <c r="AQ67" s="3"/>
+      <c r="AR67" s="3"/>
     </row>
-    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7566,8 +7728,11 @@
       <c r="AQ68" s="3">
         <v>0</v>
       </c>
+      <c r="AR68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7691,112 +7856,115 @@
       <c r="AQ69" s="3">
         <v>0</v>
       </c>
+      <c r="AR69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>663300</v>
+      </c>
+      <c r="E70" s="3">
         <v>674900</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>687000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>676300</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>690700</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>655400</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>654700</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>697300</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>688300</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>695700</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>713300</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>696400</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>711400</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>696200</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>693400</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>686500</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>696100</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>684800</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>697400</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>697800</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>681300</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>707300</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>728900</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>722200</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>739200</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>739500</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>734400</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>781000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>747000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>725200</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>716900</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>684500</v>
-      </c>
-      <c r="AI70" s="3">
-        <v>709100</v>
       </c>
       <c r="AJ70" s="3">
         <v>709100</v>
       </c>
       <c r="AK70" s="3">
-        <v>701000</v>
+        <v>709100</v>
       </c>
       <c r="AL70" s="3">
         <v>701000</v>
@@ -7805,7 +7973,7 @@
         <v>701000</v>
       </c>
       <c r="AN70" s="3">
-        <v>723700</v>
+        <v>701000</v>
       </c>
       <c r="AO70" s="3">
         <v>723700</v>
@@ -7816,8 +7984,11 @@
       <c r="AQ70" s="3">
         <v>723700</v>
       </c>
+      <c r="AR70" s="3">
+        <v>723700</v>
+      </c>
     </row>
-    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7941,133 +8112,139 @@
       <c r="AQ71" s="3">
         <v>0</v>
       </c>
+      <c r="AR71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1903400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1961500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1991100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1887400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1867500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1692700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1708300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1736600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1676100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1728100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1943800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1346900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1645500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1642300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1850600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1689300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1746200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1650300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1816100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1748900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1359700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1393600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1412900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1261100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1176300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1125000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1134400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1260200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-1238700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-1199400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-1138600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-986100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-952300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-879300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-899700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-785900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-716700</v>
-      </c>
-      <c r="AN72" s="3">
-        <v>-716800</v>
       </c>
       <c r="AO72" s="3">
         <v>-716800</v>
       </c>
       <c r="AP72" s="3">
+        <v>-716800</v>
+      </c>
+      <c r="AQ72" s="3">
         <v>-775100</v>
       </c>
-      <c r="AQ72" s="3">
+      <c r="AR72" s="3">
         <v>-756700</v>
       </c>
     </row>
-    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8191,8 +8368,11 @@
       <c r="AQ73" s="3">
         <v>0</v>
       </c>
+      <c r="AR73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8316,8 +8496,11 @@
       <c r="AQ74" s="3">
         <v>0</v>
       </c>
+      <c r="AR74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8441,133 +8624,139 @@
       <c r="AQ75" s="3">
         <v>0</v>
       </c>
+      <c r="AR75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>590800</v>
+      </c>
+      <c r="E76" s="3">
         <v>333100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>333300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>425000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>467100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>549600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>558800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>645500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>620300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>639500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>450500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>702300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>402500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>328200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>123700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>434300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>467000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>547400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>473800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>508900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>904700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1049700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1091000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1319400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1554600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1609400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1574200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1627400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1520200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1489600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1564000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1615400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1772100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1828500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1774200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1824100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1885800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1993600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1973600</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>1894500</v>
       </c>
-      <c r="AQ76" s="3">
+      <c r="AR76" s="3">
         <v>1907500</v>
       </c>
     </row>
-    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8691,263 +8880,272 @@
       <c r="AQ77" s="3">
         <v>0</v>
       </c>
+      <c r="AR77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
-      <c r="AQ80" s="2">
+      <c r="AR80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E81" s="3">
         <v>9300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-26300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-35200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-72600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>32000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-27100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>50400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>163900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-44700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>285300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>55900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>217300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-120000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>44500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-59100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>135200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-57700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-368900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-22500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-129200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-104300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-47100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>21200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>51500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>42300</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
       <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-50000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-92900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-62500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-79000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>48900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-107900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-20100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-13400</v>
       </c>
-      <c r="AN81" s="3">
-        <v>0</v>
-      </c>
       <c r="AO81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP81" s="3">
         <v>46900</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-9200</v>
       </c>
-      <c r="AQ81" s="3">
+      <c r="AR81" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8991,133 +9189,137 @@
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
       <c r="AQ82" s="3"/>
+      <c r="AR82" s="3"/>
     </row>
-    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E83" s="3">
         <v>101600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>73000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>98400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>95700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>91600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>71200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>103500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>130600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>130100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>107100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>130400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>89300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>93700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>138400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>130400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>85000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>85100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>107400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>425200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>125100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>153200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>178700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>149500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>147500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>144400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>144200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>146700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>137200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>133900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>142300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>130800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>137000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>121200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>148100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>131000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>128700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>122900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>158300</v>
-      </c>
-      <c r="AP83" s="3">
-        <v>123700</v>
       </c>
       <c r="AQ83" s="3">
         <v>123700</v>
       </c>
+      <c r="AR83" s="3">
+        <v>123700</v>
+      </c>
     </row>
-    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9241,8 +9443,11 @@
       <c r="AQ84" s="3">
         <v>0</v>
       </c>
+      <c r="AR84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9366,8 +9571,11 @@
       <c r="AQ85" s="3">
         <v>0</v>
       </c>
+      <c r="AR85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9491,8 +9699,11 @@
       <c r="AQ86" s="3">
         <v>0</v>
       </c>
+      <c r="AR86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9616,8 +9827,11 @@
       <c r="AQ87" s="3">
         <v>0</v>
       </c>
+      <c r="AR87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9741,133 +9955,139 @@
       <c r="AQ88" s="3">
         <v>0</v>
       </c>
+      <c r="AR88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E89" s="3">
         <v>88100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>168500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>180200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>115100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>149400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>169500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>78900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>180200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>234700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>503400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>341500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>258400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>148700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-95300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>327900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>40000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>701500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>57900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>193000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>85100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>197000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>95000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>168000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>141100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>271900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>204600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>63100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>100500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>115500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>78300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>319900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>60300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>149600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>46900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>215900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>93700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>175200</v>
       </c>
-      <c r="AQ89" s="3">
+      <c r="AR89" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9911,133 +10131,137 @@
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
       <c r="AQ90" s="3"/>
+      <c r="AR90" s="3"/>
     </row>
-    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-19300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-66400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-38100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-53500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-22300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-77100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-54800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-42400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-50200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-177200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-122000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-145000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-209900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-441000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-284000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-131000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-93000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-141000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-128000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-86100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-73600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-162500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-98900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-58900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-56500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-138000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-79600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-87200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-26200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-76900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-67600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-45200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-17300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-53600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-81100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-72200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-49200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-83700</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-76800</v>
       </c>
-      <c r="AQ91" s="3">
+      <c r="AR91" s="3">
         <v>-62200</v>
       </c>
     </row>
-    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -10161,8 +10385,11 @@
       <c r="AQ92" s="3">
         <v>0</v>
       </c>
+      <c r="AR92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10286,133 +10513,139 @@
       <c r="AQ93" s="3">
         <v>0</v>
       </c>
+      <c r="AR93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-66600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-84600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-72500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-41800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-223800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-68800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-34300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-42800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-168900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-165600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-139700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-134500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-294400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-127500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-69500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-52300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-199900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-149600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-83300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-246800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-125700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-85500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-74600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-148900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-75400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-140400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-40800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-76100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-98100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-79800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-39900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>224000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-107900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-55100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>3800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-65300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-76100</v>
       </c>
-      <c r="AQ94" s="3">
+      <c r="AR94" s="3">
         <v>-58400</v>
       </c>
     </row>
-    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10456,133 +10689,137 @@
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
       <c r="AQ95" s="3"/>
+      <c r="AR95" s="3"/>
     </row>
-    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E96" s="3">
         <v>13600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>13900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>13600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>13200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>12500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>11800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>14100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>13200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>12600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>10600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>10300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>11300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>11100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-9600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-10200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-9600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-10200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-8100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-27400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-8700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-9400</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-8600</v>
       </c>
       <c r="AC96" s="3">
         <v>-8600</v>
       </c>
       <c r="AD96" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-9500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-8500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-9100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-8300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-9000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-8200</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-8900</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-8200</v>
-      </c>
-      <c r="AN96" s="3">
-        <v>-9200</v>
       </c>
       <c r="AO96" s="3">
         <v>-9200</v>
       </c>
       <c r="AP96" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-8500</v>
       </c>
-      <c r="AQ96" s="3">
+      <c r="AR96" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10706,8 +10943,11 @@
       <c r="AQ97" s="3">
         <v>0</v>
       </c>
+      <c r="AR97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10831,8 +11071,11 @@
       <c r="AQ98" s="3">
         <v>0</v>
       </c>
+      <c r="AR98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10956,379 +11199,391 @@
       <c r="AQ99" s="3">
         <v>0</v>
       </c>
+      <c r="AR99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E100" s="3">
         <v>27200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-88200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-117700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-84300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>26400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>30600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-65100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-97200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-84200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-739800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-129400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-86800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-122000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>265000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-83100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-70200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-77100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>60700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-269600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-52800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-150200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>496000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-60600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-73800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-153900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>74100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-98700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>15100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-28900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-37100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-154300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-268700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-115400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-13400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-328900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-67600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>86000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-49900</v>
       </c>
-      <c r="AQ100" s="3">
+      <c r="AR100" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>5300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>5200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>5200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3700</v>
-      </c>
-      <c r="T101" s="3">
-        <v>700</v>
       </c>
       <c r="U101" s="3">
         <v>700</v>
       </c>
       <c r="V101" s="3">
+        <v>700</v>
+      </c>
+      <c r="W101" s="3">
         <v>-3000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>3100</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>8</v>
+      <c r="AE101" s="3">
+        <v>0</v>
       </c>
       <c r="AF101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
+      <c r="AG101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>800</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
         <v>0</v>
       </c>
       <c r="AL101" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="AM101" s="3">
         <v>-700</v>
       </c>
       <c r="AN101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AO101" s="3">
         <v>800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-800</v>
       </c>
-      <c r="AP101" s="3">
-        <v>0</v>
-      </c>
       <c r="AQ101" s="3">
         <v>0</v>
       </c>
+      <c r="AR101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E102" s="3">
         <v>49400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7900</v>
       </c>
-      <c r="G102" s="3">
-        <v>-11000</v>
-      </c>
       <c r="H102" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I102" s="3">
         <v>-68900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-44500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>37000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-49700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>52400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-668600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>206200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-222800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>83500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>234100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-59800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-238700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>199200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-98500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>279300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-41300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>335000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>10000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-63600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-57300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>66300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>97800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>78500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>15400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-20300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-155100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>11300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>168900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>27500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-337900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>152900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>113700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>49200</v>
       </c>
-      <c r="AQ102" s="3">
+      <c r="AR102" s="3">
         <v>48400</v>
       </c>
     </row>
